--- a/data/IKPA_MARET_2025.xlsx
+++ b/data/IKPA_MARET_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE72"/>
+  <dimension ref="A1:AE69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1055,7 +1055,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1096,10 +1096,10 @@
         <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -1108,10 +1108,10 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1146,33 +1146,33 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>7922720000</v>
+        <v>120508100000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>692725</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RUPBASAN KELAS II BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1213,10 +1213,10 @@
         <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
@@ -1225,10 +1225,10 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1263,26 +1263,26 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>16287530000</v>
+        <v>4331410000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA (692725)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3755,17 +3755,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>692725</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>RUPBASAN KELAS II BATURAJA</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3837,26 +3837,26 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>120508100000</v>
+        <v>16287530000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>RUPBASAN BATURAJA (692725)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
@@ -3980,7 +3980,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3994,12 +3994,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>4331410000</v>
+        <v>7922720000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
@@ -5150,7 +5150,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5159,17 +5159,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5191,10 +5191,10 @@
         <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41" t="n">
         <v>100</v>
@@ -5203,10 +5203,10 @@
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q41" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5241,33 +5241,33 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>11034290000</v>
+        <v>39702950000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5276,17 +5276,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5308,10 +5308,10 @@
         <v>100</v>
       </c>
       <c r="L42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>100</v>
@@ -5320,10 +5320,10 @@
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q42" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5358,26 +5358,26 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>54874670000</v>
+        <v>11034290000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
@@ -5735,7 +5735,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5749,12 +5749,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>39702950000</v>
+        <v>54874670000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5835,17 +5835,17 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -5969,7 +5969,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>2118900000</v>
+        <v>14033680000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6069,24 +6069,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -6177,33 +6177,33 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>2419220000</v>
+        <v>362218840000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418461)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6217,12 +6217,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>5939530000</v>
+        <v>2118900000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -6303,24 +6303,24 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6329,17 +6329,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -6361,10 +6361,10 @@
         <v>100</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N51" t="n">
         <v>100</v>
@@ -6373,10 +6373,10 @@
         <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q51" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -6411,33 +6411,33 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>6237000000</v>
+        <v>68569900000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6446,17 +6446,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>43919620000</v>
+        <v>21417640000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -6537,24 +6537,24 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>15638220000</v>
+        <v>9588820000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -6654,24 +6654,24 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6680,17 +6680,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -6762,33 +6762,33 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>14033680000</v>
+        <v>84332150000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -6879,33 +6879,33 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>9588820000</v>
+        <v>15638220000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6914,17 +6914,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>21417640000</v>
+        <v>43919620000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -7005,24 +7005,24 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7031,17 +7031,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -7063,10 +7063,10 @@
         <v>100</v>
       </c>
       <c r="L57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>100</v>
@@ -7075,10 +7075,10 @@
         <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q57" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -7113,33 +7113,33 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>68569900000</v>
+        <v>6237000000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7148,17 +7148,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -7230,33 +7230,33 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>84332150000</v>
+        <v>5939530000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7270,12 +7270,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>418461</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -7347,26 +7347,26 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>362218840000</v>
+        <v>2419220000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>KEMENAG OKU (418461)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -8089,12 +8089,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -8166,7 +8166,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>4578360000</v>
+        <v>4828470000</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -8175,17 +8175,17 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
@@ -8206,12 +8206,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>4828470000</v>
+        <v>4578360000</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -8292,17 +8292,17 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr"/>
@@ -8318,33 +8318,33 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>500163</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G68" t="n">
         <v>100</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I68" t="n">
         <v>100</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K68" t="n">
         <v>100</v>
@@ -8356,22 +8356,22 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O68" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="P68" t="n">
-        <v>55</v>
+        <v>62.5</v>
       </c>
       <c r="Q68" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>78.56999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8400,26 +8400,26 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>29630013990000</v>
+        <v>13807420000</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM (500163)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr"/>
@@ -8435,17 +8435,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>600092</t>
+          <t>691653</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
+          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -8455,7 +8455,7 @@
         <v>100</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
         <v>100</v>
@@ -8473,13 +8473,13 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O69" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="Q69" t="n">
         <v>70</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>78.56999999999999</v>
+        <v>42.86</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>2025</v>
       </c>
       <c r="V69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -8517,380 +8517,29 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>7084942300000</v>
+        <v>30994940000</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
+          <t>DISNAKERTRANS OKUT</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS (600092)</t>
+          <t>DISNAKERTRANS OKUT (691653)</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
+          <t>DISNAKERTRANS OKUT</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>700283</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>50</v>
-      </c>
-      <c r="G70" t="n">
-        <v>100</v>
-      </c>
-      <c r="H70" t="n">
-        <v>100</v>
-      </c>
-      <c r="I70" t="n">
-        <v>100</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>100</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>100</v>
-      </c>
-      <c r="P70" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>70</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>78.56999999999999</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>MARET</t>
-        </is>
-      </c>
-      <c r="U70" t="n">
-        <v>2025</v>
-      </c>
-      <c r="V70" t="n">
-        <v>9</v>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Upload</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>MARET 2025</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="Z70" t="n">
-        <v>6242381860000</v>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>BESAR</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN (700283)</t>
-        </is>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
-        </is>
-      </c>
-      <c r="AE70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>025</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>662127</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>100</v>
-      </c>
-      <c r="G71" t="n">
-        <v>100</v>
-      </c>
-      <c r="H71" t="n">
-        <v>30</v>
-      </c>
-      <c r="I71" t="n">
-        <v>100</v>
-      </c>
-      <c r="J71" t="n">
-        <v>100</v>
-      </c>
-      <c r="K71" t="n">
-        <v>100</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>100</v>
-      </c>
-      <c r="O71" t="n">
-        <v>30</v>
-      </c>
-      <c r="P71" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>80</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>78.13</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>MARET</t>
-        </is>
-      </c>
-      <c r="U71" t="n">
-        <v>2025</v>
-      </c>
-      <c r="V71" t="n">
-        <v>10</v>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Upload</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>MARET 2025</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="Z71" t="n">
-        <v>13807420000</v>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>KECIL</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>MAN 1 OKUS</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>MAN 1 OKUS (662127)</t>
-        </is>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>MAN 1 OKUS</t>
-        </is>
-      </c>
-      <c r="AE71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>691653</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>100</v>
-      </c>
-      <c r="G72" t="n">
-        <v>100</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>100</v>
-      </c>
-      <c r="J72" t="n">
-        <v>100</v>
-      </c>
-      <c r="K72" t="n">
-        <v>100</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>100</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>70</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>MARET</t>
-        </is>
-      </c>
-      <c r="U72" t="n">
-        <v>2025</v>
-      </c>
-      <c r="V72" t="n">
-        <v>11</v>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Upload</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>MARET 2025</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="Z72" t="n">
-        <v>30994940000</v>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>SEDANG</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>DISNAKERTRANS OKUT</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>DISNAKERTRANS OKUT (691653)</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>DISNAKERTRANS OKUT</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/IKPA_MARET_2025.xlsx
+++ b/data/IKPA_MARET_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE69"/>
+  <dimension ref="A1:AE72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,17 +596,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -653,7 +653,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -669,42 +669,42 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>123756590000</v>
+        <v>39702950000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -718,19 +718,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>440507</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="H3" t="n">
         <v>100</v>
@@ -742,7 +742,7 @@
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -757,7 +757,7 @@
         <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>80</v>
+        <v>79.92</v>
       </c>
       <c r="Q3" t="n">
         <v>80</v>
@@ -766,18 +766,18 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U3" t="n">
         <v>2025</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -786,42 +786,42 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>16429790000</v>
+        <v>1557980000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>KEMENAG OKUS (440507)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -830,24 +830,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
@@ -859,13 +859,13 @@
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -874,27 +874,27 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>80</v>
+        <v>99.36</v>
       </c>
       <c r="Q4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>99.36</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>2025</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -903,42 +903,42 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>15662930000</v>
+        <v>1200000000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -947,24 +947,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
@@ -976,13 +976,13 @@
         <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>94.42</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -991,27 +991,27 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>80</v>
+        <v>98.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>98.88</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U5" t="n">
         <v>2025</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1020,16 +1020,16 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>9643050000</v>
+        <v>1456250000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1038,24 +1038,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1064,24 +1064,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>95.34</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>98.03</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
@@ -1090,10 +1090,10 @@
         <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>100</v>
+        <v>90.67</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>92.12</v>
       </c>
       <c r="L6" t="n">
         <v>100</v>
@@ -1108,7 +1108,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>97.02</v>
       </c>
       <c r="Q6" t="n">
         <v>100</v>
@@ -1117,18 +1117,18 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>97.02</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>2025</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1137,42 +1137,42 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>120508100000</v>
+        <v>776000000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1181,24 +1181,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>100</v>
+        <v>91.78</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
@@ -1207,16 +1207,16 @@
         <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>100</v>
+        <v>83.55</v>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
@@ -1225,27 +1225,27 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>80</v>
+        <v>96.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>96.88</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U7" t="n">
         <v>2025</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1254,42 +1254,42 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>4331410000</v>
+        <v>120508100000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1298,36 +1298,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>100</v>
+        <v>92.19</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>99.23</v>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>100</v>
+        <v>84.38</v>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>100</v>
@@ -1339,10 +1339,10 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>100</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>100</v>
+        <v>96.33</v>
       </c>
       <c r="Q8" t="n">
         <v>100</v>
@@ -1351,18 +1351,18 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>96.33</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U8" t="n">
         <v>2025</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1371,16 +1371,16 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>729713950000</v>
+        <v>105503460000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1389,24 +1389,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1415,24 +1415,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>88.27</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -1441,10 +1441,10 @@
         <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>100</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1453,33 +1453,33 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>100</v>
+        <v>94.2</v>
       </c>
       <c r="O9" t="n">
         <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>70</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U9" t="n">
         <v>2025</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1488,16 +1488,16 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>66363460000</v>
+        <v>45032380000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1506,24 +1506,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1532,24 +1532,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>692725</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>RUPBASAN KELAS II BATURAJA</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>100</v>
+        <v>88.09</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
@@ -1558,45 +1558,45 @@
         <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>100</v>
+        <v>76.17</v>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>93.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>93.84</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U10" t="n">
         <v>2025</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1605,16 +1605,16 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>66147600000</v>
+        <v>16287530000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1623,24 +1623,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>RUPBASAN BATURAJA (692725)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1649,24 +1649,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>85.28</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
@@ -1675,10 +1675,10 @@
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>100</v>
+        <v>88.48</v>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>76.33</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1687,13 +1687,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>100</v>
+        <v>94.22</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>80</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>80</v>
@@ -1702,18 +1702,18 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U11" t="n">
         <v>2025</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1722,16 +1722,16 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>5600400000</v>
+        <v>5094620000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1740,24 +1740,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,24 +1766,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>418461</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>85.64</v>
       </c>
       <c r="G12" t="n">
-        <v>100</v>
+        <v>80.37</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1792,45 +1792,45 @@
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>100</v>
+        <v>71.27</v>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>67.12</v>
       </c>
       <c r="L12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>100</v>
+        <v>93.62</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>100</v>
+        <v>68.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U12" t="n">
         <v>2025</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1839,42 +1839,42 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>740697110000</v>
+        <v>2419220000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>KEMENAG OKU (418461)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1883,71 +1883,71 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>666507</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>100</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>100</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>78.89</v>
       </c>
       <c r="L13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>100</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>100</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>100</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U13" t="n">
         <v>2025</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1956,42 +1956,42 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>547904240000</v>
+        <v>2455820000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>POLRES OKUS (665307)</t>
+          <t>KEMENAG OKUT (666507)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2000,17 +2000,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2020,7 +2020,7 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>100</v>
@@ -2032,39 +2032,39 @@
         <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14" t="n">
         <v>100</v>
       </c>
       <c r="O14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Q14" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U14" t="n">
         <v>2025</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>576761480000</v>
+        <v>46323370000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2117,27 +2117,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>100</v>
+        <v>99.37</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>100</v>
@@ -2146,42 +2146,42 @@
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>97.47</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" t="n">
         <v>100</v>
       </c>
       <c r="O15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>80</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U15" t="n">
         <v>2025</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2190,42 +2190,42 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>27113310000</v>
+        <v>88187740000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2234,27 +2234,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>100</v>
@@ -2263,42 +2263,42 @@
         <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>96.81</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N16" t="n">
         <v>100</v>
       </c>
       <c r="O16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>80</v>
+        <v>74.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>74.36</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U16" t="n">
         <v>2025</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2307,42 +2307,42 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>3054130000</v>
+        <v>54874670000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2351,27 +2351,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>100</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>100</v>
@@ -2380,42 +2380,42 @@
         <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17" t="n">
         <v>100</v>
       </c>
       <c r="O17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>80</v>
+        <v>73.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>73.77</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U17" t="n">
         <v>2025</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2424,42 +2424,42 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>1299340000</v>
+        <v>52449290000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2468,27 +2468,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>98.41</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>100</v>
@@ -2497,42 +2497,42 @@
         <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18" t="n">
         <v>100</v>
       </c>
       <c r="O18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>80</v>
+        <v>73.73</v>
       </c>
       <c r="Q18" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>73.73</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U18" t="n">
         <v>2025</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2541,42 +2541,42 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>5531600000</v>
+        <v>547904240000</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2585,27 +2585,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>666507</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>100</v>
@@ -2614,42 +2614,42 @@
         <v>100</v>
       </c>
       <c r="K19" t="n">
-        <v>100</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19" t="n">
         <v>100</v>
       </c>
       <c r="O19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>80</v>
+        <v>73.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>73.64</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U19" t="n">
         <v>2025</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2658,42 +2658,42 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>2455820000</v>
+        <v>67301000000</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666507)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>100</v>
@@ -2731,7 +2731,7 @@
         <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L20" t="n">
         <v>100</v>
@@ -2743,10 +2743,10 @@
         <v>100</v>
       </c>
       <c r="O20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>100</v>
+        <v>73.64</v>
       </c>
       <c r="Q20" t="n">
         <v>100</v>
@@ -2755,18 +2755,18 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>73.64</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U20" t="n">
         <v>2025</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2775,42 +2775,42 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>52449290000</v>
+        <v>88015540000</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2819,36 +2819,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>100</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>100</v>
+        <v>91.98</v>
       </c>
       <c r="K21" t="n">
-        <v>100</v>
+        <v>98.97</v>
       </c>
       <c r="L21" t="n">
         <v>100</v>
@@ -2860,10 +2860,10 @@
         <v>100</v>
       </c>
       <c r="O21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>100</v>
+        <v>73.59</v>
       </c>
       <c r="Q21" t="n">
         <v>100</v>
@@ -2872,18 +2872,18 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>73.59</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U21" t="n">
         <v>2025</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2892,42 +2892,42 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>67301000000</v>
+        <v>729713950000</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2936,27 +2936,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>100</v>
+        <v>97.95</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>100</v>
@@ -2965,42 +2965,42 @@
         <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>100</v>
+        <v>91.81</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22" t="n">
         <v>100</v>
       </c>
       <c r="O22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>80</v>
+        <v>73.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>73.36</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U22" t="n">
         <v>2025</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3009,42 +3009,42 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>70843010000</v>
+        <v>68569900000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3053,71 +3053,71 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>100</v>
+        <v>93.05</v>
       </c>
       <c r="G23" t="n">
-        <v>100</v>
+        <v>99.48</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>100</v>
       </c>
       <c r="J23" t="n">
-        <v>100</v>
+        <v>86.09</v>
       </c>
       <c r="K23" t="n">
-        <v>100</v>
+        <v>97.92</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N23" t="n">
         <v>100</v>
       </c>
       <c r="O23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>80</v>
+        <v>72.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>100</v>
+        <v>72.5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U23" t="n">
         <v>2025</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3126,16 +3126,16 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>69434110000</v>
+        <v>123756590000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3144,24 +3144,24 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3170,71 +3170,71 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>100</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>100</v>
       </c>
       <c r="J24" t="n">
-        <v>100</v>
+        <v>81.98</v>
       </c>
       <c r="K24" t="n">
-        <v>100</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="L24" t="n">
         <v>100</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
         <v>100</v>
       </c>
       <c r="O24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>90</v>
+        <v>71.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>100</v>
+        <v>71.87</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U24" t="n">
         <v>2025</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3243,42 +3243,42 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>127924290000</v>
+        <v>69434110000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3287,36 +3287,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
+        <v>89.53</v>
       </c>
       <c r="G25" t="n">
-        <v>100</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>100</v>
       </c>
       <c r="J25" t="n">
-        <v>100</v>
+        <v>79.06</v>
       </c>
       <c r="K25" t="n">
-        <v>100</v>
+        <v>99.73</v>
       </c>
       <c r="L25" t="n">
         <v>100</v>
@@ -3328,10 +3328,10 @@
         <v>100</v>
       </c>
       <c r="O25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>100</v>
+        <v>71.81</v>
       </c>
       <c r="Q25" t="n">
         <v>100</v>
@@ -3340,18 +3340,18 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>71.81</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U25" t="n">
         <v>2025</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>75395210000</v>
+        <v>81909970000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3378,24 +3378,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3404,36 +3404,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>100</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>100</v>
+        <v>96.89</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>100</v>
       </c>
       <c r="J26" t="n">
-        <v>100</v>
+        <v>85.98</v>
       </c>
       <c r="K26" t="n">
-        <v>100</v>
+        <v>93.53</v>
       </c>
       <c r="L26" t="n">
         <v>100</v>
@@ -3442,13 +3442,13 @@
         <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>100</v>
+        <v>94.03</v>
       </c>
       <c r="O26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>100</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="Q26" t="n">
         <v>100</v>
@@ -3457,18 +3457,18 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U26" t="n">
         <v>2025</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3477,42 +3477,42 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>88187740000</v>
+        <v>70843010000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3526,31 +3526,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>100</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>100</v>
+        <v>98.58</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>100</v>
       </c>
       <c r="J27" t="n">
-        <v>100</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>94.33</v>
       </c>
       <c r="L27" t="n">
         <v>100</v>
@@ -3562,10 +3562,10 @@
         <v>100</v>
       </c>
       <c r="O27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>100</v>
+        <v>70.88</v>
       </c>
       <c r="Q27" t="n">
         <v>100</v>
@@ -3574,18 +3574,18 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>100</v>
+        <v>70.88</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U27" t="n">
         <v>2025</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3594,16 +3594,16 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>100762000000</v>
+        <v>75395210000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3612,24 +3612,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3638,71 +3638,71 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>100</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>100</v>
       </c>
       <c r="J28" t="n">
-        <v>100</v>
+        <v>76.13</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
       </c>
       <c r="O28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>80</v>
+        <v>70.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>100</v>
+        <v>70.88</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U28" t="n">
         <v>2025</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3711,42 +3711,42 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>26533740000</v>
+        <v>280396970000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3755,36 +3755,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>692725</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RUPBASAN KELAS II BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>89.7</v>
       </c>
       <c r="G29" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>100</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>100</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="L29" t="n">
         <v>100</v>
@@ -3796,10 +3796,10 @@
         <v>100</v>
       </c>
       <c r="O29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>100</v>
+        <v>70.7</v>
       </c>
       <c r="Q29" t="n">
         <v>100</v>
@@ -3808,18 +3808,18 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>100</v>
+        <v>70.7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U29" t="n">
         <v>2025</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3828,42 +3828,42 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>16287530000</v>
+        <v>740697110000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA (692725)</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3877,66 +3877,66 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>100</v>
+        <v>98.59</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>100</v>
+        <v>73.64</v>
       </c>
       <c r="K30" t="n">
-        <v>100</v>
+        <v>94.88</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30" t="n">
-        <v>100</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>80</v>
+        <v>69.97</v>
       </c>
       <c r="Q30" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>100</v>
+        <v>69.97</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U30" t="n">
         <v>2025</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3945,16 +3945,16 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>1557980000</v>
+        <v>15638220000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3963,24 +3963,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440507)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3989,71 +3989,71 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>84.7</v>
       </c>
       <c r="G31" t="n">
-        <v>100</v>
+        <v>99.19</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>100</v>
+        <v>69.39</v>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N31" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="O31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>80</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>100</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U31" t="n">
         <v>2025</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4062,42 +4062,42 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>7922720000</v>
+        <v>84332150000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4106,36 +4106,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>691653</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>33.33</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="I32" t="n">
         <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="K32" t="n">
-        <v>100</v>
+        <v>33.33</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4144,33 +4144,33 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="P32" t="n">
-        <v>80</v>
+        <v>48.54</v>
       </c>
       <c r="Q32" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>69.34</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U32" t="n">
         <v>2025</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4179,42 +4179,42 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>356160000</v>
+        <v>30994940000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>DISNAKERTRANS OKUT</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>DISNAKERTRANS OKUT (691653)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>DISNAKERTRANS OKUT</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4223,71 +4223,71 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>100</v>
+        <v>90.45</v>
       </c>
       <c r="G33" t="n">
-        <v>100</v>
+        <v>96.44</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>100</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>100</v>
+        <v>85.75</v>
       </c>
       <c r="L33" t="n">
         <v>100</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N33" t="n">
         <v>100</v>
       </c>
       <c r="O33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>90</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="Q33" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U33" t="n">
         <v>2025</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4296,42 +4296,42 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>88015540000</v>
+        <v>14033680000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4340,36 +4340,36 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>100</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>100</v>
+        <v>97.89</v>
       </c>
       <c r="L34" t="n">
         <v>100</v>
@@ -4378,33 +4378,33 @@
         <v>100</v>
       </c>
       <c r="N34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>100</v>
+        <v>62.22</v>
       </c>
       <c r="Q34" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>100</v>
+        <v>69.14</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U34" t="n">
         <v>2025</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4413,16 +4413,16 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>105503460000</v>
+        <v>400061720000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -4431,24 +4431,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4457,71 +4457,71 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>100</v>
+        <v>88.81</v>
       </c>
       <c r="G35" t="n">
-        <v>100</v>
+        <v>96.13</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>100</v>
       </c>
       <c r="J35" t="n">
-        <v>100</v>
+        <v>77.61</v>
       </c>
       <c r="K35" t="n">
-        <v>100</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N35" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="O35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>90</v>
+        <v>68.91</v>
       </c>
       <c r="Q35" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>100</v>
+        <v>68.91</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U35" t="n">
         <v>2025</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4530,42 +4530,42 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>81909970000</v>
+        <v>21417640000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4574,71 +4574,71 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>100</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J36" t="n">
-        <v>100</v>
+        <v>74.63</v>
       </c>
       <c r="K36" t="n">
-        <v>100</v>
+        <v>94.61</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N36" t="n">
         <v>100</v>
       </c>
       <c r="O36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>80</v>
+        <v>68.12</v>
       </c>
       <c r="Q36" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>100</v>
+        <v>68.12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U36" t="n">
         <v>2025</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4647,42 +4647,42 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>5094620000</v>
+        <v>100762000000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4696,22 +4696,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>100</v>
@@ -4720,7 +4720,7 @@
         <v>100</v>
       </c>
       <c r="K37" t="n">
-        <v>100</v>
+        <v>97.52</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4729,13 +4729,13 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>100</v>
+        <v>99.27</v>
       </c>
       <c r="O37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>80</v>
+        <v>54.43</v>
       </c>
       <c r="Q37" t="n">
         <v>80</v>
@@ -4744,18 +4744,18 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U37" t="n">
         <v>2025</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4764,16 +4764,16 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>1411480000</v>
+        <v>356160000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4782,24 +4782,24 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4808,71 +4808,71 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>100</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>94.66</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>100</v>
+        <v>76.92</v>
       </c>
       <c r="K38" t="n">
-        <v>100</v>
+        <v>85.78</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N38" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="O38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>80</v>
+        <v>67.98</v>
       </c>
       <c r="Q38" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>100</v>
+        <v>67.98</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U38" t="n">
         <v>2025</v>
       </c>
       <c r="V38" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4881,42 +4881,42 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>13241640000</v>
+        <v>127924290000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4925,27 +4925,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>97.69</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>100</v>
@@ -4954,42 +4954,42 @@
         <v>100</v>
       </c>
       <c r="K39" t="n">
-        <v>100</v>
+        <v>95.38</v>
       </c>
       <c r="L39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>100</v>
       </c>
       <c r="O39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>90</v>
+        <v>54.08</v>
       </c>
       <c r="Q39" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>100</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U39" t="n">
         <v>2025</v>
       </c>
       <c r="V39" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4998,42 +4998,42 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>280396970000</v>
+        <v>15662930000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5042,27 +5042,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>100</v>
+        <v>97.03</v>
       </c>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>100</v>
@@ -5071,42 +5071,42 @@
         <v>100</v>
       </c>
       <c r="K40" t="n">
-        <v>100</v>
+        <v>94.06</v>
       </c>
       <c r="L40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
       </c>
       <c r="O40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>100</v>
+        <v>53.81</v>
       </c>
       <c r="Q40" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>100</v>
+        <v>67.27</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U40" t="n">
         <v>2025</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5115,42 +5115,42 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>46323370000</v>
+        <v>11034290000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5159,27 +5159,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>100</v>
       </c>
       <c r="G41" t="n">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>100</v>
@@ -5188,42 +5188,42 @@
         <v>100</v>
       </c>
       <c r="K41" t="n">
-        <v>100</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>100</v>
+        <v>87.84</v>
       </c>
       <c r="O41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>100</v>
+        <v>53.78</v>
       </c>
       <c r="Q41" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>100</v>
+        <v>67.22</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U41" t="n">
         <v>2025</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5232,42 +5232,42 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>39702950000</v>
+        <v>576761480000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5281,31 +5281,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
+        <v>94.87</v>
       </c>
       <c r="G42" t="n">
-        <v>100</v>
+        <v>99.41</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>100</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5317,10 +5317,10 @@
         <v>100</v>
       </c>
       <c r="O42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>80</v>
+        <v>53.23</v>
       </c>
       <c r="Q42" t="n">
         <v>80</v>
@@ -5329,18 +5329,18 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>100</v>
+        <v>66.53</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U42" t="n">
         <v>2025</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5349,42 +5349,42 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>11034290000</v>
+        <v>513916100000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5393,71 +5393,71 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>100</v>
+        <v>95.92</v>
       </c>
       <c r="G43" t="n">
-        <v>100</v>
+        <v>98.55</v>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>100</v>
+        <v>91.83</v>
       </c>
       <c r="K43" t="n">
-        <v>100</v>
+        <v>97.09</v>
       </c>
       <c r="L43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>100</v>
       </c>
       <c r="O43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>100</v>
+        <v>53.19</v>
       </c>
       <c r="Q43" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>100</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U43" t="n">
         <v>2025</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5466,16 +5466,16 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>1200000000</v>
+        <v>1411480000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5484,24 +5484,24 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5510,71 +5510,71 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>100</v>
+        <v>96.16</v>
       </c>
       <c r="G44" t="n">
-        <v>100</v>
+        <v>96.56</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>100</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>100</v>
+        <v>93.11</v>
       </c>
       <c r="L44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>100</v>
       </c>
       <c r="O44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>100</v>
+        <v>52.47</v>
       </c>
       <c r="Q44" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>65.59</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U44" t="n">
         <v>2025</v>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5583,16 +5583,16 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>1456250000</v>
+        <v>4578360000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -5601,24 +5601,24 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5627,71 +5627,71 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>100</v>
+        <v>98.36</v>
       </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>100</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>100</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>100</v>
       </c>
       <c r="O45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>100</v>
+        <v>65.5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U45" t="n">
         <v>2025</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5700,42 +5700,42 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>776000000</v>
+        <v>65740740000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5744,71 +5744,71 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>100</v>
+        <v>96.06</v>
       </c>
       <c r="G46" t="n">
-        <v>100</v>
+        <v>96.23</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>100</v>
+        <v>92.12</v>
       </c>
       <c r="K46" t="n">
-        <v>100</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>100</v>
       </c>
       <c r="O46" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>100</v>
+        <v>52.31</v>
       </c>
       <c r="Q46" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>100</v>
+        <v>65.39</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U46" t="n">
         <v>2025</v>
       </c>
       <c r="V46" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5817,16 +5817,16 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>54874670000</v>
+        <v>26533740000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5835,24 +5835,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5866,31 +5866,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>100</v>
+        <v>96.53</v>
       </c>
       <c r="G47" t="n">
-        <v>100</v>
+        <v>94.22</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>100</v>
+        <v>93.05</v>
       </c>
       <c r="K47" t="n">
-        <v>100</v>
+        <v>94.88</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5899,13 +5899,13 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>100</v>
+        <v>93.56</v>
       </c>
       <c r="O47" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>80</v>
+        <v>52.29</v>
       </c>
       <c r="Q47" t="n">
         <v>80</v>
@@ -5914,18 +5914,18 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>100</v>
+        <v>65.36</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U47" t="n">
         <v>2025</v>
       </c>
       <c r="V47" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5934,42 +5934,42 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>15314690000</v>
+        <v>1299340000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5983,28 +5983,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>90.89</v>
       </c>
       <c r="G48" t="n">
         <v>100</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>100</v>
+        <v>81.78</v>
       </c>
       <c r="K48" t="n">
         <v>100</v>
@@ -6019,10 +6019,10 @@
         <v>100</v>
       </c>
       <c r="O48" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>80</v>
+        <v>52.27</v>
       </c>
       <c r="Q48" t="n">
         <v>80</v>
@@ -6031,18 +6031,18 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>100</v>
+        <v>65.33</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U48" t="n">
         <v>2025</v>
       </c>
       <c r="V48" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6051,16 +6051,16 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>14033680000</v>
+        <v>5531600000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6069,24 +6069,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6100,31 +6100,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>100</v>
+        <v>93.56</v>
       </c>
       <c r="G49" t="n">
-        <v>100</v>
+        <v>97.95</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>100</v>
+        <v>87.11</v>
       </c>
       <c r="K49" t="n">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6136,10 +6136,10 @@
         <v>100</v>
       </c>
       <c r="O49" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>80</v>
+        <v>52.25</v>
       </c>
       <c r="Q49" t="n">
         <v>80</v>
@@ -6148,18 +6148,18 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>100</v>
+        <v>65.31</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U49" t="n">
         <v>2025</v>
       </c>
       <c r="V49" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6168,42 +6168,42 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>362218840000</v>
+        <v>6237000000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6217,31 +6217,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>100</v>
+        <v>96.91</v>
       </c>
       <c r="H50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>100</v>
+        <v>89.13</v>
       </c>
       <c r="K50" t="n">
-        <v>100</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -6250,13 +6250,13 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>100</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>80</v>
+        <v>52.21</v>
       </c>
       <c r="Q50" t="n">
         <v>80</v>
@@ -6265,18 +6265,18 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>100</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U50" t="n">
         <v>2025</v>
       </c>
       <c r="V50" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6285,16 +6285,16 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>2118900000</v>
+        <v>4828470000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -6303,24 +6303,24 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6329,71 +6329,71 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>93.42</v>
       </c>
       <c r="G51" t="n">
-        <v>100</v>
+        <v>96.25</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>100</v>
+        <v>86.83</v>
       </c>
       <c r="K51" t="n">
-        <v>100</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>100</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>100</v>
+        <v>52.08</v>
       </c>
       <c r="Q51" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>100</v>
+        <v>65.09</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U51" t="n">
         <v>2025</v>
       </c>
       <c r="V51" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6402,42 +6402,42 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>68569900000</v>
+        <v>66147600000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6451,31 +6451,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>97.17</v>
       </c>
       <c r="G52" t="n">
-        <v>100</v>
+        <v>94.8</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>100</v>
+        <v>94.33</v>
       </c>
       <c r="K52" t="n">
-        <v>100</v>
+        <v>89.59</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -6487,10 +6487,10 @@
         <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>80</v>
+        <v>52.07</v>
       </c>
       <c r="Q52" t="n">
         <v>80</v>
@@ -6499,18 +6499,18 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>100</v>
+        <v>65.08</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U52" t="n">
         <v>2025</v>
       </c>
       <c r="V52" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6519,16 +6519,16 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>21417640000</v>
+        <v>18460870000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -6537,24 +6537,24 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6568,31 +6568,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>93.36</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>97.03</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
+        <v>86.72</v>
       </c>
       <c r="K53" t="n">
-        <v>100</v>
+        <v>94.05</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -6604,10 +6604,10 @@
         <v>100</v>
       </c>
       <c r="O53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>80</v>
+        <v>51.82</v>
       </c>
       <c r="Q53" t="n">
         <v>80</v>
@@ -6616,18 +6616,18 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>100</v>
+        <v>64.77</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U53" t="n">
         <v>2025</v>
       </c>
       <c r="V53" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6636,16 +6636,16 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>9588820000</v>
+        <v>13807420000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -6654,24 +6654,24 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6680,36 +6680,36 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>100</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>100</v>
+        <v>94.84</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -6718,13 +6718,13 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>100</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>80</v>
+        <v>51.63</v>
       </c>
       <c r="Q54" t="n">
         <v>80</v>
@@ -6733,18 +6733,18 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>100</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U54" t="n">
         <v>2025</v>
       </c>
       <c r="V54" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6753,42 +6753,42 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>84332150000</v>
+        <v>5600400000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6802,31 +6802,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>90.31</v>
       </c>
       <c r="G55" t="n">
-        <v>100</v>
+        <v>96.64</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>100</v>
+        <v>80.61</v>
       </c>
       <c r="K55" t="n">
-        <v>100</v>
+        <v>99.98</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -6835,13 +6835,13 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>100</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>80</v>
+        <v>51.42</v>
       </c>
       <c r="Q55" t="n">
         <v>80</v>
@@ -6850,18 +6850,18 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>100</v>
+        <v>64.27</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U55" t="n">
         <v>2025</v>
       </c>
       <c r="V55" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6870,42 +6870,42 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>15638220000</v>
+        <v>362218840000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6914,36 +6914,36 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>94.03</v>
       </c>
       <c r="G56" t="n">
-        <v>100</v>
+        <v>94.89</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>100</v>
+        <v>88.06</v>
       </c>
       <c r="K56" t="n">
-        <v>100</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6952,13 +6952,13 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>100</v>
+        <v>99.81</v>
       </c>
       <c r="O56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>80</v>
+        <v>51.18</v>
       </c>
       <c r="Q56" t="n">
         <v>80</v>
@@ -6967,18 +6967,18 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>100</v>
+        <v>63.98</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U56" t="n">
         <v>2025</v>
       </c>
       <c r="V56" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6987,42 +6987,42 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>43919620000</v>
+        <v>10141880000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7036,22 +7036,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>100</v>
+        <v>88.19</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>100</v>
@@ -7060,7 +7060,7 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>100</v>
+        <v>84.83</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -7069,13 +7069,13 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>100</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>80</v>
+        <v>51.12</v>
       </c>
       <c r="Q57" t="n">
         <v>80</v>
@@ -7084,18 +7084,18 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>100</v>
+        <v>63.9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U57" t="n">
         <v>2025</v>
       </c>
       <c r="V57" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7104,16 +7104,16 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>6237000000</v>
+        <v>3054130000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -7122,24 +7122,24 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7162,22 +7162,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>90.94</v>
       </c>
       <c r="G58" t="n">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
+        <v>81.88</v>
       </c>
       <c r="K58" t="n">
-        <v>100</v>
+        <v>92.78</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -7186,13 +7186,13 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>100</v>
+        <v>99.61</v>
       </c>
       <c r="O58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>80</v>
+        <v>50.8</v>
       </c>
       <c r="Q58" t="n">
         <v>80</v>
@@ -7201,18 +7201,18 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>100</v>
+        <v>63.5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U58" t="n">
         <v>2025</v>
       </c>
       <c r="V58" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7221,12 +7221,12 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z58" t="n">
@@ -7256,7 +7256,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7270,31 +7270,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>91.23</v>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>95.52</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>100</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>100</v>
+        <v>91.03</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -7306,10 +7306,10 @@
         <v>100</v>
       </c>
       <c r="O59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>80</v>
+        <v>50.58</v>
       </c>
       <c r="Q59" t="n">
         <v>80</v>
@@ -7318,18 +7318,18 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>100</v>
+        <v>63.22</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U59" t="n">
         <v>2025</v>
       </c>
       <c r="V59" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7338,35 +7338,35 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>2419220000</v>
+        <v>16429790000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418461)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7382,36 +7382,36 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>100</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>95.88</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>100</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>100</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -7420,13 +7420,13 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>100</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="O60" t="n">
-        <v>95.88</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>78.97</v>
+        <v>50.52</v>
       </c>
       <c r="Q60" t="n">
         <v>80</v>
@@ -7435,18 +7435,18 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>98.70999999999999</v>
+        <v>63.16</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U60" t="n">
         <v>2025</v>
       </c>
       <c r="V60" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7455,16 +7455,16 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>18460870000</v>
+        <v>66363460000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7499,36 +7499,36 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>100</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>95.33</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>100</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>100</v>
+        <v>96.08</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -7540,10 +7540,10 @@
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>95.33</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>78.83</v>
+        <v>50.32</v>
       </c>
       <c r="Q61" t="n">
         <v>80</v>
@@ -7552,18 +7552,18 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>98.54000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U61" t="n">
         <v>2025</v>
       </c>
       <c r="V61" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7572,35 +7572,35 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>45032380000</v>
+        <v>2118900000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7616,71 +7616,71 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>100</v>
+        <v>88.36</v>
       </c>
       <c r="G62" t="n">
-        <v>100</v>
+        <v>95.47</v>
       </c>
       <c r="H62" t="n">
-        <v>87.83</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>100</v>
+        <v>76.72</v>
       </c>
       <c r="K62" t="n">
-        <v>100</v>
+        <v>96.66</v>
       </c>
       <c r="L62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>100</v>
+        <v>94.27</v>
       </c>
       <c r="O62" t="n">
-        <v>87.83</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>86.95999999999999</v>
+        <v>50.27</v>
       </c>
       <c r="Q62" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>96.62</v>
+        <v>62.83</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U62" t="n">
         <v>2025</v>
       </c>
       <c r="V62" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7689,35 +7689,35 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>400061720000</v>
+        <v>9588820000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7738,31 +7738,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>87.16</v>
       </c>
       <c r="G63" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>100</v>
+        <v>74.31</v>
       </c>
       <c r="K63" t="n">
-        <v>100</v>
+        <v>95.78</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -7771,13 +7771,13 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>100</v>
+        <v>94.02</v>
       </c>
       <c r="O63" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>76.5</v>
+        <v>49.7</v>
       </c>
       <c r="Q63" t="n">
         <v>80</v>
@@ -7786,18 +7786,18 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>95.63</v>
+        <v>62.13</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U63" t="n">
         <v>2025</v>
       </c>
       <c r="V63" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7806,35 +7806,35 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>513916100000</v>
+        <v>4331410000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -7855,31 +7855,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="G64" t="n">
-        <v>100</v>
+        <v>91.39</v>
       </c>
       <c r="H64" t="n">
-        <v>82.5</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>100</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>100</v>
+        <v>82.77</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -7891,10 +7891,10 @@
         <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>82.5</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>75.63</v>
+        <v>49.6</v>
       </c>
       <c r="Q64" t="n">
         <v>80</v>
@@ -7903,18 +7903,18 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>94.53</v>
+        <v>62</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U64" t="n">
         <v>2025</v>
       </c>
       <c r="V64" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7923,16 +7923,16 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>10141880000</v>
+        <v>9643050000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
@@ -7967,36 +7967,36 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>100</v>
+        <v>82.19</v>
       </c>
       <c r="G65" t="n">
-        <v>100</v>
+        <v>98.08</v>
       </c>
       <c r="H65" t="n">
-        <v>76.67</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>100</v>
       </c>
       <c r="J65" t="n">
-        <v>100</v>
+        <v>64.38</v>
       </c>
       <c r="K65" t="n">
-        <v>100</v>
+        <v>97.11</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -8005,13 +8005,13 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>100</v>
+        <v>99.05</v>
       </c>
       <c r="O65" t="n">
-        <v>76.67</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>74.17</v>
+        <v>48.98</v>
       </c>
       <c r="Q65" t="n">
         <v>80</v>
@@ -8020,18 +8020,18 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>92.70999999999999</v>
+        <v>61.23</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U65" t="n">
         <v>2025</v>
       </c>
       <c r="V65" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8040,35 +8040,35 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>65740740000</v>
+        <v>13241640000</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
@@ -8089,31 +8089,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>100</v>
+        <v>89.95</v>
       </c>
       <c r="G66" t="n">
-        <v>100</v>
+        <v>90.72</v>
       </c>
       <c r="H66" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>100</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>100</v>
+        <v>81.83</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -8122,13 +8122,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="O66" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>71.25</v>
+        <v>48.31</v>
       </c>
       <c r="Q66" t="n">
         <v>80</v>
@@ -8137,18 +8137,18 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>89.06</v>
+        <v>60.39</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U66" t="n">
         <v>2025</v>
       </c>
       <c r="V66" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8157,35 +8157,35 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>4828470000</v>
+        <v>27113310000</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
@@ -8201,36 +8201,36 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>999</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>700283</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G67" t="n">
-        <v>100</v>
+        <v>33.33</v>
       </c>
       <c r="H67" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I67" t="n">
         <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>100</v>
+        <v>33.33</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -8239,33 +8239,33 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P67" t="n">
-        <v>71.25</v>
+        <v>41.67</v>
       </c>
       <c r="Q67" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>89.06</v>
+        <v>59.52</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U67" t="n">
         <v>2025</v>
       </c>
       <c r="V67" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -8274,35 +8274,35 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>4578360000</v>
+        <v>6242381860000</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN (700283)</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr"/>
@@ -8318,36 +8318,36 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>100</v>
+        <v>85.73</v>
       </c>
       <c r="G68" t="n">
-        <v>100</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>100</v>
       </c>
       <c r="J68" t="n">
-        <v>100</v>
+        <v>71.45</v>
       </c>
       <c r="K68" t="n">
-        <v>100</v>
+        <v>98.16</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8356,13 +8356,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>100</v>
+        <v>71.86</v>
       </c>
       <c r="O68" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>62.5</v>
+        <v>47.54</v>
       </c>
       <c r="Q68" t="n">
         <v>80</v>
@@ -8371,18 +8371,18 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>78.13</v>
+        <v>59.42</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U68" t="n">
         <v>2025</v>
       </c>
       <c r="V68" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -8391,35 +8391,35 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>13807420000</v>
+        <v>43919620000</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr"/>
@@ -8435,24 +8435,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>691653</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>50</v>
+        <v>85.88</v>
       </c>
       <c r="G69" t="n">
-        <v>100</v>
+        <v>88.23</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -8461,10 +8461,10 @@
         <v>100</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>71.75</v>
       </c>
       <c r="K69" t="n">
-        <v>100</v>
+        <v>87.42</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -8473,33 +8473,33 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>100</v>
+        <v>89.03</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>30</v>
+        <v>47.15</v>
       </c>
       <c r="Q69" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>42.86</v>
+        <v>58.94</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>MARET</t>
+          <t>JULI</t>
         </is>
       </c>
       <c r="U69" t="n">
         <v>2025</v>
       </c>
       <c r="V69" t="n">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -8508,38 +8508,389 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>MARET 2025</t>
+          <t>JULI 2025</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>30994940000</v>
+        <v>7922720000</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>DISNAKERTRANS OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>DISNAKERTRANS OKUT (691653)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>DISNAKERTRANS OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>418457</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>88.39</v>
+      </c>
+      <c r="G70" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>100</v>
+      </c>
+      <c r="J70" t="n">
+        <v>76.77</v>
+      </c>
+      <c r="K70" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>80.37</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>80</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>JULI</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>2025</v>
+      </c>
+      <c r="V70" t="n">
+        <v>67</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>JULI 2025</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>15314690000</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>KECIL</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU (418457)</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>KEMENAG OKU</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>600092</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>50</v>
+      </c>
+      <c r="G71" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>100</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>70</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>JULI</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>2025</v>
+      </c>
+      <c r="V71" t="n">
+        <v>68</v>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>JULI 2025</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>7084942300000</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS (600092)</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>500163</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>50</v>
+      </c>
+      <c r="G72" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>100</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>70</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>JULI</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>2025</v>
+      </c>
+      <c r="V72" t="n">
+        <v>68</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>JULI 2025</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>29630013990000</v>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>BESAR</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM (500163)</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/IKPA_MARET_2025.xlsx
+++ b/data/IKPA_MARET_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE72"/>
+  <dimension ref="A1:AE69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,17 +596,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -653,7 +653,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -669,42 +669,42 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>39702950000</v>
+        <v>123756590000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -718,19 +718,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>440507</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
         <v>100</v>
@@ -742,7 +742,7 @@
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -757,7 +757,7 @@
         <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>79.92</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="n">
         <v>80</v>
@@ -766,18 +766,18 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U3" t="n">
         <v>2025</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -786,42 +786,42 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>1557980000</v>
+        <v>16429790000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440507)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -830,24 +830,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>99.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
@@ -859,13 +859,13 @@
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>96.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -874,27 +874,27 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>99.36</v>
+        <v>80</v>
       </c>
       <c r="Q4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>99.36</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>2025</v>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -903,42 +903,42 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>1200000000</v>
+        <v>15662930000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -947,24 +947,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>98.61</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
@@ -976,13 +976,13 @@
         <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>94.42</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>100</v>
@@ -991,27 +991,27 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>98.88</v>
+        <v>80</v>
       </c>
       <c r="Q5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>98.88</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U5" t="n">
         <v>2025</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1020,16 +1020,16 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>1456250000</v>
+        <v>9643050000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1038,24 +1038,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1064,24 +1064,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>95.34</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>98.03</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
@@ -1090,10 +1090,10 @@
         <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>90.67</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>92.12</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
         <v>100</v>
@@ -1108,7 +1108,7 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>97.02</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="n">
         <v>100</v>
@@ -1117,18 +1117,18 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>97.02</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>2025</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1137,42 +1137,42 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>776000000</v>
+        <v>120508100000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1181,24 +1181,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>91.78</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>99.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
@@ -1207,16 +1207,16 @@
         <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>83.55</v>
+        <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>96.72</v>
+        <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>100</v>
@@ -1225,27 +1225,27 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>96.88</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U7" t="n">
         <v>2025</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1254,42 +1254,42 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>120508100000</v>
+        <v>4331410000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1298,36 +1298,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>92.19</v>
+        <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>99.23</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>97.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
         <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>96.93000000000001</v>
+        <v>100</v>
       </c>
       <c r="L8" t="n">
         <v>100</v>
@@ -1339,10 +1339,10 @@
         <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>97.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>96.33</v>
+        <v>100</v>
       </c>
       <c r="Q8" t="n">
         <v>100</v>
@@ -1351,18 +1351,18 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>96.33</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U8" t="n">
         <v>2025</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1371,16 +1371,16 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>105503460000</v>
+        <v>729713950000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1389,24 +1389,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1415,24 +1415,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>88.27</v>
+        <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>96.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -1441,10 +1441,10 @@
         <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>76.54000000000001</v>
+        <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>98.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1453,33 +1453,33 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="O9" t="n">
         <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>75.54000000000001</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>94.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U9" t="n">
         <v>2025</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1488,16 +1488,16 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>45032380000</v>
+        <v>66363460000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1506,24 +1506,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1532,24 +1532,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>692725</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RUPBASAN KELAS II BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>88.09</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
@@ -1558,45 +1558,45 @@
         <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>76.17</v>
+        <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="O10" t="n">
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>93.84</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>93.84</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U10" t="n">
         <v>2025</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1605,16 +1605,16 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>16287530000</v>
+        <v>66147600000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1623,24 +1623,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA (692725)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>RUPBASAN BATURAJA</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1649,24 +1649,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>94.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>85.28</v>
+        <v>100</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
@@ -1675,10 +1675,10 @@
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>88.48</v>
+        <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>76.33</v>
+        <v>100</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1687,13 +1687,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>94.22</v>
+        <v>100</v>
       </c>
       <c r="O11" t="n">
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>72.95999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="n">
         <v>80</v>
@@ -1702,18 +1702,18 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>91.2</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U11" t="n">
         <v>2025</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1722,16 +1722,16 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>5094620000</v>
+        <v>5600400000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1740,24 +1740,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,24 +1766,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>85.64</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>80.37</v>
+        <v>100</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1792,45 +1792,45 @@
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>71.27</v>
+        <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>67.12</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>93.62</v>
+        <v>100</v>
       </c>
       <c r="O12" t="n">
         <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>68.48</v>
+        <v>100</v>
       </c>
       <c r="Q12" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>85.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U12" t="n">
         <v>2025</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1839,42 +1839,42 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>2419220000</v>
+        <v>740697110000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418461)</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1883,71 +1883,71 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>666507</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>79.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>87.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="I13" t="n">
         <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>83.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>78.89</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>79.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="O13" t="n">
-        <v>87.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>67.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>84.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U13" t="n">
         <v>2025</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1956,42 +1956,42 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>2455820000</v>
+        <v>547904240000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666507)</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2000,17 +2000,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2020,7 +2020,7 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
         <v>100</v>
@@ -2032,39 +2032,39 @@
         <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>100</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U14" t="n">
         <v>2025</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>46323370000</v>
+        <v>576761480000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2117,27 +2117,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>99.37</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
         <v>100</v>
@@ -2146,42 +2146,42 @@
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>97.47</v>
+        <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>100</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" t="n">
-        <v>74.48999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>74.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U15" t="n">
         <v>2025</v>
       </c>
       <c r="V15" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2190,42 +2190,42 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>88187740000</v>
+        <v>27113310000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2234,27 +2234,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
         <v>100</v>
@@ -2263,42 +2263,42 @@
         <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>96.81</v>
+        <v>100</v>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>100</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>74.36</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>74.36</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U16" t="n">
         <v>2025</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2307,42 +2307,42 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>54874670000</v>
+        <v>3054130000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2351,27 +2351,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>98.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
         <v>100</v>
@@ -2380,42 +2380,42 @@
         <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>93.84999999999999</v>
+        <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>100</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>73.77</v>
+        <v>80</v>
       </c>
       <c r="Q17" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>73.77</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U17" t="n">
         <v>2025</v>
       </c>
       <c r="V17" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2424,42 +2424,42 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>52449290000</v>
+        <v>1299340000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2468,27 +2468,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>98.41</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
         <v>100</v>
@@ -2497,42 +2497,42 @@
         <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>93.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>100</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18" t="n">
-        <v>73.73</v>
+        <v>80</v>
       </c>
       <c r="Q18" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>73.73</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U18" t="n">
         <v>2025</v>
       </c>
       <c r="V18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2541,42 +2541,42 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>547904240000</v>
+        <v>5531600000</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>POLRES OKUS (665307)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2585,27 +2585,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>666507</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
         <v>100</v>
@@ -2614,42 +2614,42 @@
         <v>100</v>
       </c>
       <c r="K19" t="n">
-        <v>93.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="L19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>100</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>73.64</v>
+        <v>80</v>
       </c>
       <c r="Q19" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>73.64</v>
+        <v>100</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U19" t="n">
         <v>2025</v>
       </c>
       <c r="V19" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2658,42 +2658,42 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>67301000000</v>
+        <v>2455820000</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>KEMENAG OKUT (666507)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
         <v>100</v>
@@ -2731,7 +2731,7 @@
         <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="L20" t="n">
         <v>100</v>
@@ -2743,10 +2743,10 @@
         <v>100</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>73.64</v>
+        <v>100</v>
       </c>
       <c r="Q20" t="n">
         <v>100</v>
@@ -2755,18 +2755,18 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>73.64</v>
+        <v>100</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U20" t="n">
         <v>2025</v>
       </c>
       <c r="V20" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2775,42 +2775,42 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>88015540000</v>
+        <v>52449290000</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2819,36 +2819,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>95.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>99.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>91.98</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
-        <v>98.97</v>
+        <v>100</v>
       </c>
       <c r="L21" t="n">
         <v>100</v>
@@ -2860,10 +2860,10 @@
         <v>100</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>73.59</v>
+        <v>100</v>
       </c>
       <c r="Q21" t="n">
         <v>100</v>
@@ -2872,18 +2872,18 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>73.59</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U21" t="n">
         <v>2025</v>
       </c>
       <c r="V21" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2892,42 +2892,42 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>729713950000</v>
+        <v>67301000000</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2936,27 +2936,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>97.95</v>
+        <v>100</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
         <v>100</v>
@@ -2965,42 +2965,42 @@
         <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>91.81</v>
+        <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>100</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>73.36</v>
+        <v>80</v>
       </c>
       <c r="Q22" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>73.36</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U22" t="n">
         <v>2025</v>
       </c>
       <c r="V22" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3009,42 +3009,42 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>68569900000</v>
+        <v>70843010000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3053,71 +3053,71 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>93.05</v>
+        <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>99.48</v>
+        <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
         <v>100</v>
       </c>
       <c r="J23" t="n">
-        <v>86.09</v>
+        <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>97.92</v>
+        <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>100</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23" t="n">
-        <v>72.5</v>
+        <v>80</v>
       </c>
       <c r="Q23" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>72.5</v>
+        <v>100</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U23" t="n">
         <v>2025</v>
       </c>
       <c r="V23" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3126,16 +3126,16 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>123756590000</v>
+        <v>69434110000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3144,24 +3144,24 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3170,71 +3170,71 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>90.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>99.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
         <v>100</v>
       </c>
       <c r="J24" t="n">
-        <v>81.98</v>
+        <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>97.84999999999999</v>
+        <v>100</v>
       </c>
       <c r="L24" t="n">
         <v>100</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>100</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>71.87</v>
+        <v>90</v>
       </c>
       <c r="Q24" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>71.87</v>
+        <v>100</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U24" t="n">
         <v>2025</v>
       </c>
       <c r="V24" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3243,42 +3243,42 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>69434110000</v>
+        <v>127924290000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3287,36 +3287,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>89.53</v>
+        <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>99.93000000000001</v>
+        <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
         <v>100</v>
       </c>
       <c r="J25" t="n">
-        <v>79.06</v>
+        <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>99.73</v>
+        <v>100</v>
       </c>
       <c r="L25" t="n">
         <v>100</v>
@@ -3328,10 +3328,10 @@
         <v>100</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>71.81</v>
+        <v>100</v>
       </c>
       <c r="Q25" t="n">
         <v>100</v>
@@ -3340,18 +3340,18 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>71.81</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U25" t="n">
         <v>2025</v>
       </c>
       <c r="V25" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>81909970000</v>
+        <v>75395210000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3378,24 +3378,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3404,36 +3404,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>92.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>96.89</v>
+        <v>100</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
         <v>100</v>
       </c>
       <c r="J26" t="n">
-        <v>85.98</v>
+        <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>93.53</v>
+        <v>100</v>
       </c>
       <c r="L26" t="n">
         <v>100</v>
@@ -3442,13 +3442,13 @@
         <v>100</v>
       </c>
       <c r="N26" t="n">
-        <v>94.03</v>
+        <v>100</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>71.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q26" t="n">
         <v>100</v>
@@ -3457,18 +3457,18 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>71.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U26" t="n">
         <v>2025</v>
       </c>
       <c r="V26" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3477,42 +3477,42 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>70843010000</v>
+        <v>88187740000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3526,31 +3526,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>90.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>98.58</v>
+        <v>100</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
         <v>100</v>
       </c>
       <c r="J27" t="n">
-        <v>80.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>94.33</v>
+        <v>100</v>
       </c>
       <c r="L27" t="n">
         <v>100</v>
@@ -3562,10 +3562,10 @@
         <v>100</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27" t="n">
-        <v>70.88</v>
+        <v>100</v>
       </c>
       <c r="Q27" t="n">
         <v>100</v>
@@ -3574,18 +3574,18 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>70.88</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U27" t="n">
         <v>2025</v>
       </c>
       <c r="V27" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3594,16 +3594,16 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>75395210000</v>
+        <v>100762000000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3612,24 +3612,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3638,71 +3638,71 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>88.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>99.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
         <v>100</v>
       </c>
       <c r="J28" t="n">
-        <v>76.13</v>
+        <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>97.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>70.88</v>
+        <v>80</v>
       </c>
       <c r="Q28" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>70.88</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U28" t="n">
         <v>2025</v>
       </c>
       <c r="V28" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3711,42 +3711,42 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>280396970000</v>
+        <v>26533740000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3755,36 +3755,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>692725</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>RUPBASAN KELAS II BATURAJA</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>89.7</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>98.48</v>
+        <v>100</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
         <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>79.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>93.93000000000001</v>
+        <v>100</v>
       </c>
       <c r="L29" t="n">
         <v>100</v>
@@ -3796,10 +3796,10 @@
         <v>100</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>70.7</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="n">
         <v>100</v>
@@ -3808,18 +3808,18 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>70.7</v>
+        <v>100</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U29" t="n">
         <v>2025</v>
       </c>
       <c r="V29" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3828,42 +3828,42 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>740697110000</v>
+        <v>16287530000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>RUPBASAN BATURAJA (692725)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>RUPBASAN BATURAJA</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3877,66 +3877,66 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>440507</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>86.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>98.59</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>73.64</v>
+        <v>100</v>
       </c>
       <c r="K30" t="n">
-        <v>94.88</v>
+        <v>100</v>
       </c>
       <c r="L30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>99.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>69.97</v>
+        <v>80</v>
       </c>
       <c r="Q30" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>69.97</v>
+        <v>100</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U30" t="n">
         <v>2025</v>
       </c>
       <c r="V30" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3945,16 +3945,16 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>15638220000</v>
+        <v>1557980000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3963,24 +3963,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>KEMENAG OKUS (440507)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3989,71 +3989,71 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>84.7</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>99.19</v>
+        <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31" t="n">
         <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>69.39</v>
+        <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>97.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="L31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>69.79000000000001</v>
+        <v>80</v>
       </c>
       <c r="Q31" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>69.79000000000001</v>
+        <v>100</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U31" t="n">
         <v>2025</v>
       </c>
       <c r="V31" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4062,42 +4062,42 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>84332150000</v>
+        <v>7922720000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4106,36 +4106,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>691653</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>33.33</v>
+        <v>100</v>
       </c>
       <c r="H32" t="n">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="I32" t="n">
         <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>33.33</v>
+        <v>100</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4144,33 +4144,33 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32" t="n">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>48.54</v>
+        <v>80</v>
       </c>
       <c r="Q32" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>69.34</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U32" t="n">
         <v>2025</v>
       </c>
       <c r="V32" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4179,42 +4179,42 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>30994940000</v>
+        <v>356160000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>DISNAKERTRANS OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>DISNAKERTRANS OKUT (691653)</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>DISNAKERTRANS OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4223,71 +4223,71 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>90.45</v>
+        <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>96.44</v>
+        <v>100</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33" t="n">
         <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>80.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>85.75</v>
+        <v>100</v>
       </c>
       <c r="L33" t="n">
         <v>100</v>
       </c>
       <c r="M33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>100</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>69.29000000000001</v>
+        <v>90</v>
       </c>
       <c r="Q33" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>69.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U33" t="n">
         <v>2025</v>
       </c>
       <c r="V33" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4296,42 +4296,42 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>14033680000</v>
+        <v>88015540000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4340,36 +4340,36 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>92.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I34" t="n">
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>84.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>97.89</v>
+        <v>100</v>
       </c>
       <c r="L34" t="n">
         <v>100</v>
@@ -4378,33 +4378,33 @@
         <v>100</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>62.22</v>
+        <v>100</v>
       </c>
       <c r="Q34" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>69.14</v>
+        <v>100</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U34" t="n">
         <v>2025</v>
       </c>
       <c r="V34" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4413,16 +4413,16 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>400061720000</v>
+        <v>105503460000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -4431,24 +4431,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4457,71 +4457,71 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>88.81</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>96.13</v>
+        <v>100</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
         <v>100</v>
       </c>
       <c r="J35" t="n">
-        <v>77.61</v>
+        <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>88.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="L35" t="n">
-        <v>96.67</v>
+        <v>100</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>68.91</v>
+        <v>90</v>
       </c>
       <c r="Q35" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>68.91</v>
+        <v>100</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U35" t="n">
         <v>2025</v>
       </c>
       <c r="V35" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4530,42 +4530,42 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>21417640000</v>
+        <v>81909970000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4574,71 +4574,71 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>77.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>98.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I36" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" t="n">
+        <v>100</v>
+      </c>
+      <c r="K36" t="n">
+        <v>100</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>100</v>
+      </c>
+      <c r="O36" t="n">
+        <v>100</v>
+      </c>
+      <c r="P36" t="n">
         <v>80</v>
       </c>
-      <c r="J36" t="n">
-        <v>74.63</v>
-      </c>
-      <c r="K36" t="n">
-        <v>94.61</v>
-      </c>
-      <c r="L36" t="n">
-        <v>100</v>
-      </c>
-      <c r="M36" t="n">
-        <v>100</v>
-      </c>
-      <c r="N36" t="n">
-        <v>100</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>68.12</v>
-      </c>
       <c r="Q36" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>68.12</v>
+        <v>100</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U36" t="n">
         <v>2025</v>
       </c>
       <c r="V36" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4647,42 +4647,42 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>100762000000</v>
+        <v>5094620000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4696,22 +4696,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
         <v>100</v>
@@ -4720,7 +4720,7 @@
         <v>100</v>
       </c>
       <c r="K37" t="n">
-        <v>97.52</v>
+        <v>100</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4729,13 +4729,13 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>99.27</v>
+        <v>100</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>54.43</v>
+        <v>80</v>
       </c>
       <c r="Q37" t="n">
         <v>80</v>
@@ -4744,18 +4744,18 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>68.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U37" t="n">
         <v>2025</v>
       </c>
       <c r="V37" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4764,16 +4764,16 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>356160000</v>
+        <v>1411480000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4782,24 +4782,24 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4808,71 +4808,71 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>88.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>94.66</v>
+        <v>100</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>76.92</v>
+        <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>85.78</v>
+        <v>100</v>
       </c>
       <c r="L38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>92.86</v>
+        <v>100</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>67.98</v>
+        <v>80</v>
       </c>
       <c r="Q38" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>67.98</v>
+        <v>100</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U38" t="n">
         <v>2025</v>
       </c>
       <c r="V38" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4881,42 +4881,42 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>127924290000</v>
+        <v>13241640000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4925,27 +4925,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>97.69</v>
+        <v>100</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
         <v>100</v>
@@ -4954,42 +4954,42 @@
         <v>100</v>
       </c>
       <c r="K39" t="n">
-        <v>95.38</v>
+        <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N39" t="n">
         <v>100</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>54.08</v>
+        <v>90</v>
       </c>
       <c r="Q39" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>67.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U39" t="n">
         <v>2025</v>
       </c>
       <c r="V39" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4998,42 +4998,42 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>15662930000</v>
+        <v>280396970000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5042,27 +5042,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>97.03</v>
+        <v>100</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I40" t="n">
         <v>100</v>
@@ -5071,42 +5071,42 @@
         <v>100</v>
       </c>
       <c r="K40" t="n">
-        <v>94.06</v>
+        <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N40" t="n">
         <v>100</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>53.81</v>
+        <v>100</v>
       </c>
       <c r="Q40" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>67.27</v>
+        <v>100</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U40" t="n">
         <v>2025</v>
       </c>
       <c r="V40" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5115,42 +5115,42 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>11034290000</v>
+        <v>46323370000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5159,27 +5159,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>100</v>
       </c>
       <c r="G41" t="n">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I41" t="n">
         <v>100</v>
@@ -5188,42 +5188,42 @@
         <v>100</v>
       </c>
       <c r="K41" t="n">
-        <v>99.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41" t="n">
-        <v>87.84</v>
+        <v>100</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>53.78</v>
+        <v>100</v>
       </c>
       <c r="Q41" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>67.22</v>
+        <v>100</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U41" t="n">
         <v>2025</v>
       </c>
       <c r="V41" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5232,42 +5232,42 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>576761480000</v>
+        <v>39702950000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5281,31 +5281,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>94.87</v>
+        <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>99.41</v>
+        <v>100</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>89.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="K42" t="n">
-        <v>98.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5317,10 +5317,10 @@
         <v>100</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>53.23</v>
+        <v>80</v>
       </c>
       <c r="Q42" t="n">
         <v>80</v>
@@ -5329,18 +5329,18 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>66.53</v>
+        <v>100</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U42" t="n">
         <v>2025</v>
       </c>
       <c r="V42" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5349,42 +5349,42 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>513916100000</v>
+        <v>11034290000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5393,71 +5393,71 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>95.92</v>
+        <v>100</v>
       </c>
       <c r="G43" t="n">
-        <v>98.55</v>
+        <v>100</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I43" t="n">
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>91.83</v>
+        <v>100</v>
       </c>
       <c r="K43" t="n">
-        <v>97.09</v>
+        <v>100</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N43" t="n">
         <v>100</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>53.19</v>
+        <v>100</v>
       </c>
       <c r="Q43" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>66.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U43" t="n">
         <v>2025</v>
       </c>
       <c r="V43" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5466,16 +5466,16 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>1411480000</v>
+        <v>1200000000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5484,24 +5484,24 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5510,71 +5510,71 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>96.16</v>
+        <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>96.56</v>
+        <v>100</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
         <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>92.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>93.11</v>
+        <v>100</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N44" t="n">
         <v>100</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>52.47</v>
+        <v>100</v>
       </c>
       <c r="Q44" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>65.59</v>
+        <v>100</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U44" t="n">
         <v>2025</v>
       </c>
       <c r="V44" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5583,16 +5583,16 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>4578360000</v>
+        <v>1456250000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -5601,24 +5601,24 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5627,71 +5627,71 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>93.54000000000001</v>
+        <v>100</v>
       </c>
       <c r="G45" t="n">
-        <v>98.36</v>
+        <v>100</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" t="n">
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>87.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="K45" t="n">
-        <v>96.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N45" t="n">
         <v>100</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="Q45" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>65.5</v>
+        <v>100</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U45" t="n">
         <v>2025</v>
       </c>
       <c r="V45" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5700,42 +5700,42 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>65740740000</v>
+        <v>776000000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5744,71 +5744,71 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>96.06</v>
+        <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>96.23</v>
+        <v>100</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I46" t="n">
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>92.12</v>
+        <v>100</v>
       </c>
       <c r="K46" t="n">
-        <v>92.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N46" t="n">
         <v>100</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>52.31</v>
+        <v>100</v>
       </c>
       <c r="Q46" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>65.39</v>
+        <v>100</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U46" t="n">
         <v>2025</v>
       </c>
       <c r="V46" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5817,16 +5817,16 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>26533740000</v>
+        <v>54874670000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5835,24 +5835,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5866,31 +5866,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>96.53</v>
+        <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>94.22</v>
+        <v>100</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
         <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>93.05</v>
+        <v>100</v>
       </c>
       <c r="K47" t="n">
-        <v>94.88</v>
+        <v>100</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5899,13 +5899,13 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>93.56</v>
+        <v>100</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>52.29</v>
+        <v>80</v>
       </c>
       <c r="Q47" t="n">
         <v>80</v>
@@ -5914,18 +5914,18 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>65.36</v>
+        <v>100</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U47" t="n">
         <v>2025</v>
       </c>
       <c r="V47" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5934,42 +5934,42 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>1299340000</v>
+        <v>15314690000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5983,28 +5983,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>90.89</v>
+        <v>100</v>
       </c>
       <c r="G48" t="n">
         <v>100</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I48" t="n">
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>81.78</v>
+        <v>100</v>
       </c>
       <c r="K48" t="n">
         <v>100</v>
@@ -6019,10 +6019,10 @@
         <v>100</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>52.27</v>
+        <v>80</v>
       </c>
       <c r="Q48" t="n">
         <v>80</v>
@@ -6031,18 +6031,18 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>65.33</v>
+        <v>100</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U48" t="n">
         <v>2025</v>
       </c>
       <c r="V48" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6051,16 +6051,16 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>5531600000</v>
+        <v>14033680000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6069,24 +6069,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6100,31 +6100,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>93.56</v>
+        <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>97.95</v>
+        <v>100</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>87.11</v>
+        <v>100</v>
       </c>
       <c r="K49" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6136,10 +6136,10 @@
         <v>100</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>52.25</v>
+        <v>80</v>
       </c>
       <c r="Q49" t="n">
         <v>80</v>
@@ -6148,18 +6148,18 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>65.31</v>
+        <v>100</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U49" t="n">
         <v>2025</v>
       </c>
       <c r="V49" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6168,42 +6168,42 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>6237000000</v>
+        <v>362218840000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6217,31 +6217,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>94.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>96.91</v>
+        <v>100</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I50" t="n">
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>89.13</v>
+        <v>100</v>
       </c>
       <c r="K50" t="n">
-        <v>94.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -6250,13 +6250,13 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>99.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>52.21</v>
+        <v>80</v>
       </c>
       <c r="Q50" t="n">
         <v>80</v>
@@ -6265,18 +6265,18 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>65.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U50" t="n">
         <v>2025</v>
       </c>
       <c r="V50" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6285,16 +6285,16 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>4828470000</v>
+        <v>2118900000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -6303,24 +6303,24 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6329,71 +6329,71 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>93.42</v>
+        <v>100</v>
       </c>
       <c r="G51" t="n">
-        <v>96.25</v>
+        <v>100</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I51" t="n">
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>86.83</v>
+        <v>100</v>
       </c>
       <c r="K51" t="n">
-        <v>98.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N51" t="n">
-        <v>94.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>52.08</v>
+        <v>100</v>
       </c>
       <c r="Q51" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>65.09</v>
+        <v>100</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U51" t="n">
         <v>2025</v>
       </c>
       <c r="V51" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6402,42 +6402,42 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>66147600000</v>
+        <v>68569900000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6451,31 +6451,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>97.17</v>
+        <v>100</v>
       </c>
       <c r="G52" t="n">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>94.33</v>
+        <v>100</v>
       </c>
       <c r="K52" t="n">
-        <v>89.59</v>
+        <v>100</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -6487,10 +6487,10 @@
         <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>52.07</v>
+        <v>80</v>
       </c>
       <c r="Q52" t="n">
         <v>80</v>
@@ -6499,18 +6499,18 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>65.08</v>
+        <v>100</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U52" t="n">
         <v>2025</v>
       </c>
       <c r="V52" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6519,16 +6519,16 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>18460870000</v>
+        <v>21417640000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -6537,24 +6537,24 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6568,31 +6568,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>93.36</v>
+        <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>97.03</v>
+        <v>100</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>86.72</v>
+        <v>100</v>
       </c>
       <c r="K53" t="n">
-        <v>94.05</v>
+        <v>100</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -6604,10 +6604,10 @@
         <v>100</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>51.82</v>
+        <v>80</v>
       </c>
       <c r="Q53" t="n">
         <v>80</v>
@@ -6616,18 +6616,18 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>64.77</v>
+        <v>100</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U53" t="n">
         <v>2025</v>
       </c>
       <c r="V53" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6636,16 +6636,16 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>13807420000</v>
+        <v>9588820000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -6654,24 +6654,24 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6680,36 +6680,36 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>92.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="G54" t="n">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>84.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="K54" t="n">
-        <v>94.84</v>
+        <v>100</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -6718,13 +6718,13 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>99.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>51.63</v>
+        <v>80</v>
       </c>
       <c r="Q54" t="n">
         <v>80</v>
@@ -6733,18 +6733,18 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>64.54000000000001</v>
+        <v>100</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U54" t="n">
         <v>2025</v>
       </c>
       <c r="V54" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6753,42 +6753,42 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>5600400000</v>
+        <v>84332150000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6802,31 +6802,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>90.31</v>
+        <v>100</v>
       </c>
       <c r="G55" t="n">
-        <v>96.64</v>
+        <v>100</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I55" t="n">
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>80.61</v>
+        <v>100</v>
       </c>
       <c r="K55" t="n">
-        <v>99.98</v>
+        <v>100</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -6835,13 +6835,13 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>93.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>51.42</v>
+        <v>80</v>
       </c>
       <c r="Q55" t="n">
         <v>80</v>
@@ -6850,18 +6850,18 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>64.27</v>
+        <v>100</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U55" t="n">
         <v>2025</v>
       </c>
       <c r="V55" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6870,42 +6870,42 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>362218840000</v>
+        <v>15638220000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6914,36 +6914,36 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>94.03</v>
+        <v>100</v>
       </c>
       <c r="G56" t="n">
-        <v>94.89</v>
+        <v>100</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>88.06</v>
+        <v>100</v>
       </c>
       <c r="K56" t="n">
-        <v>89.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6952,13 +6952,13 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>99.81</v>
+        <v>100</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>51.18</v>
+        <v>80</v>
       </c>
       <c r="Q56" t="n">
         <v>80</v>
@@ -6967,18 +6967,18 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>63.98</v>
+        <v>100</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U56" t="n">
         <v>2025</v>
       </c>
       <c r="V56" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6987,42 +6987,42 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>10141880000</v>
+        <v>43919620000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7036,22 +7036,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>88.19</v>
+        <v>100</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I57" t="n">
         <v>100</v>
@@ -7060,7 +7060,7 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>84.83</v>
+        <v>100</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -7069,13 +7069,13 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>91.54000000000001</v>
+        <v>100</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>51.12</v>
+        <v>80</v>
       </c>
       <c r="Q57" t="n">
         <v>80</v>
@@ -7084,18 +7084,18 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>63.9</v>
+        <v>100</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U57" t="n">
         <v>2025</v>
       </c>
       <c r="V57" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7104,16 +7104,16 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>3054130000</v>
+        <v>6237000000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -7122,24 +7122,24 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7162,22 +7162,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>90.94</v>
+        <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>81.88</v>
+        <v>100</v>
       </c>
       <c r="K58" t="n">
-        <v>92.78</v>
+        <v>100</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -7186,13 +7186,13 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>99.61</v>
+        <v>100</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>50.8</v>
+        <v>80</v>
       </c>
       <c r="Q58" t="n">
         <v>80</v>
@@ -7201,18 +7201,18 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>63.5</v>
+        <v>100</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U58" t="n">
         <v>2025</v>
       </c>
       <c r="V58" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7221,12 +7221,12 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z58" t="n">
@@ -7256,7 +7256,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7270,31 +7270,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>418461</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>91.23</v>
+        <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>95.52</v>
+        <v>100</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>82.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="K59" t="n">
-        <v>91.03</v>
+        <v>100</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -7306,10 +7306,10 @@
         <v>100</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>50.58</v>
+        <v>80</v>
       </c>
       <c r="Q59" t="n">
         <v>80</v>
@@ -7318,18 +7318,18 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>63.22</v>
+        <v>100</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U59" t="n">
         <v>2025</v>
       </c>
       <c r="V59" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7338,35 +7338,35 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>16429790000</v>
+        <v>2419220000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>KEMENAG OKU (418461)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7382,36 +7382,36 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>95.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>86.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>95.88</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>90.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="K60" t="n">
-        <v>98.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -7420,13 +7420,13 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>73.93000000000001</v>
+        <v>100</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>95.88</v>
       </c>
       <c r="P60" t="n">
-        <v>50.52</v>
+        <v>78.97</v>
       </c>
       <c r="Q60" t="n">
         <v>80</v>
@@ -7435,18 +7435,18 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>63.16</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U60" t="n">
         <v>2025</v>
       </c>
       <c r="V60" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7455,16 +7455,16 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>66363460000</v>
+        <v>18460870000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7499,36 +7499,36 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>87.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="G61" t="n">
-        <v>98.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>95.33</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>74.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>96.08</v>
+        <v>100</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -7540,10 +7540,10 @@
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>95.33</v>
       </c>
       <c r="P61" t="n">
-        <v>50.32</v>
+        <v>78.83</v>
       </c>
       <c r="Q61" t="n">
         <v>80</v>
@@ -7552,18 +7552,18 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>62.9</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U61" t="n">
         <v>2025</v>
       </c>
       <c r="V61" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7572,35 +7572,35 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>2118900000</v>
+        <v>45032380000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7616,71 +7616,71 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>88.36</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>95.47</v>
+        <v>100</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>87.83</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>76.72</v>
+        <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>96.66</v>
+        <v>100</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N62" t="n">
-        <v>94.27</v>
+        <v>100</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>87.83</v>
       </c>
       <c r="P62" t="n">
-        <v>50.27</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="Q62" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>62.83</v>
+        <v>96.62</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U62" t="n">
         <v>2025</v>
       </c>
       <c r="V62" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7689,35 +7689,35 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>9588820000</v>
+        <v>400061720000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7738,31 +7738,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>87.16</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I63" t="n">
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>74.31</v>
+        <v>100</v>
       </c>
       <c r="K63" t="n">
-        <v>95.78</v>
+        <v>100</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -7771,13 +7771,13 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>94.02</v>
+        <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="P63" t="n">
-        <v>49.7</v>
+        <v>76.5</v>
       </c>
       <c r="Q63" t="n">
         <v>80</v>
@@ -7786,18 +7786,18 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>62.13</v>
+        <v>95.63</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U63" t="n">
         <v>2025</v>
       </c>
       <c r="V63" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7806,35 +7806,35 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>4331410000</v>
+        <v>513916100000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -7855,31 +7855,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>91.39</v>
+        <v>100</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>86.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="K64" t="n">
-        <v>82.77</v>
+        <v>100</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -7891,10 +7891,10 @@
         <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="P64" t="n">
-        <v>49.6</v>
+        <v>75.63</v>
       </c>
       <c r="Q64" t="n">
         <v>80</v>
@@ -7903,18 +7903,18 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>62</v>
+        <v>94.53</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U64" t="n">
         <v>2025</v>
       </c>
       <c r="V64" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7923,16 +7923,16 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>9643050000</v>
+        <v>10141880000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
@@ -7967,36 +7967,36 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>82.19</v>
+        <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>98.08</v>
+        <v>100</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>76.67</v>
       </c>
       <c r="I65" t="n">
         <v>100</v>
       </c>
       <c r="J65" t="n">
-        <v>64.38</v>
+        <v>100</v>
       </c>
       <c r="K65" t="n">
-        <v>97.11</v>
+        <v>100</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -8005,13 +8005,13 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>99.05</v>
+        <v>100</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>76.67</v>
       </c>
       <c r="P65" t="n">
-        <v>48.98</v>
+        <v>74.17</v>
       </c>
       <c r="Q65" t="n">
         <v>80</v>
@@ -8020,18 +8020,18 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>61.23</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U65" t="n">
         <v>2025</v>
       </c>
       <c r="V65" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8040,35 +8040,35 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>13241640000</v>
+        <v>65740740000</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
@@ -8089,31 +8089,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>89.95</v>
+        <v>100</v>
       </c>
       <c r="G66" t="n">
-        <v>90.72</v>
+        <v>100</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I66" t="n">
         <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>79.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K66" t="n">
-        <v>81.83</v>
+        <v>100</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -8122,13 +8122,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P66" t="n">
-        <v>48.31</v>
+        <v>71.25</v>
       </c>
       <c r="Q66" t="n">
         <v>80</v>
@@ -8137,18 +8137,18 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>60.39</v>
+        <v>89.06</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U66" t="n">
         <v>2025</v>
       </c>
       <c r="V66" t="n">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8157,35 +8157,35 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>27113310000</v>
+        <v>4828470000</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
@@ -8201,36 +8201,36 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>700283</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G67" t="n">
-        <v>33.33</v>
+        <v>100</v>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I67" t="n">
         <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K67" t="n">
-        <v>33.33</v>
+        <v>100</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -8239,33 +8239,33 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O67" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="P67" t="n">
-        <v>41.67</v>
+        <v>71.25</v>
       </c>
       <c r="Q67" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>59.52</v>
+        <v>89.06</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U67" t="n">
         <v>2025</v>
       </c>
       <c r="V67" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -8274,35 +8274,35 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>6242381860000</v>
+        <v>4578360000</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN (700283)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA PENYALUR DANA DESA, INSENTIF FISKAL, OTONOMI KHUSUS DAN KEISTIMEWAAN</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr"/>
@@ -8318,36 +8318,36 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>85.73</v>
+        <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>85.01000000000001</v>
+        <v>100</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I68" t="n">
         <v>100</v>
       </c>
       <c r="J68" t="n">
-        <v>71.45</v>
+        <v>100</v>
       </c>
       <c r="K68" t="n">
-        <v>98.16</v>
+        <v>100</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8356,13 +8356,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>71.86</v>
+        <v>100</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P68" t="n">
-        <v>47.54</v>
+        <v>62.5</v>
       </c>
       <c r="Q68" t="n">
         <v>80</v>
@@ -8371,18 +8371,18 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>59.42</v>
+        <v>78.13</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U68" t="n">
         <v>2025</v>
       </c>
       <c r="V68" t="n">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -8391,35 +8391,35 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>43919620000</v>
+        <v>13807420000</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr"/>
@@ -8435,24 +8435,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>691653</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>DINAS TENAGA KERJA DAN TRANSMIGRASI KABUPATEN OKU TIMUR</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>85.88</v>
+        <v>50</v>
       </c>
       <c r="G69" t="n">
-        <v>88.23</v>
+        <v>100</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -8461,10 +8461,10 @@
         <v>100</v>
       </c>
       <c r="J69" t="n">
-        <v>71.75</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>87.42</v>
+        <v>100</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -8473,33 +8473,33 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>89.03</v>
+        <v>100</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>47.15</v>
+        <v>30</v>
       </c>
       <c r="Q69" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>58.94</v>
+        <v>42.86</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>JULI</t>
+          <t>MARET</t>
         </is>
       </c>
       <c r="U69" t="n">
         <v>2025</v>
       </c>
       <c r="V69" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -8508,389 +8508,38 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>JULI 2025</t>
+          <t>MARET 2025</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>7922720000</v>
+        <v>30994940000</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>DISNAKERTRANS OKUT</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>DISNAKERTRANS OKUT (691653)</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>DISNAKERTRANS OKUT</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>025</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>418457</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>88.39</v>
-      </c>
-      <c r="G70" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>100</v>
-      </c>
-      <c r="J70" t="n">
-        <v>76.77</v>
-      </c>
-      <c r="K70" t="n">
-        <v>80.62</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>80.37</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>45.68</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>80</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>JULI</t>
-        </is>
-      </c>
-      <c r="U70" t="n">
-        <v>2025</v>
-      </c>
-      <c r="V70" t="n">
-        <v>67</v>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Upload</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>JULI 2025</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="Z70" t="n">
-        <v>15314690000</v>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>KECIL</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418457)</t>
-        </is>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU</t>
-        </is>
-      </c>
-      <c r="AE70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>600092</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>50</v>
-      </c>
-      <c r="G71" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>100</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>70</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>JULI</t>
-        </is>
-      </c>
-      <c r="U71" t="n">
-        <v>2025</v>
-      </c>
-      <c r="V71" t="n">
-        <v>68</v>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Upload</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>JULI 2025</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="Z71" t="n">
-        <v>7084942300000</v>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>BESAR</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS (600092)</t>
-        </is>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER KHUSUS</t>
-        </is>
-      </c>
-      <c r="AE71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>500163</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>50</v>
-      </c>
-      <c r="G72" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>100</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>70</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>JULI</t>
-        </is>
-      </c>
-      <c r="U72" t="n">
-        <v>2025</v>
-      </c>
-      <c r="V72" t="n">
-        <v>68</v>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Upload</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>JULI 2025</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="Z72" t="n">
-        <v>29630013990000</v>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>BESAR</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM (500163)</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA PENYALUR DANA TRANSFER UMUM</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
